--- a/02_Corporate_Finance/_template_BASE.xlsx
+++ b/02_Corporate_Finance/_template_BASE.xlsx
@@ -35,12 +35,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0x"/>
-    <numFmt numFmtId="168" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0x"/>
+    <numFmt numFmtId="169" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -173,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,26 +189,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -818,13 +820,13 @@
       <c r="E5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="23" t="n">
+      <c r="F5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,13 +845,13 @@
       <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="23" t="n">
+      <c r="F6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -868,13 +870,13 @@
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="23" t="n">
+      <c r="F7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -893,13 +895,13 @@
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="23" t="n">
+      <c r="F8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,13 +920,13 @@
       <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="23" t="n">
+      <c r="F9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -943,13 +945,13 @@
       <c r="E10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="23" t="n">
+      <c r="F10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -968,13 +970,13 @@
       <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="23" t="n">
+      <c r="F11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -984,27 +986,27 @@
           <t>Median</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="23">
         <f>MEDIAN(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="23">
         <f>MEDIAN(D5:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="23">
         <f>MEDIAN(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="26">
         <f>MEDIAN(F5:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="26">
         <f>MEDIAN(G5:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="26">
         <f>MEDIAN(H5:H12)</f>
         <v/>
       </c>
@@ -1041,172 +1043,172 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>WACC \ Term. growth</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="28" t="n">
         <v>0.015</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="28" t="n">
         <v>0.025</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="28" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="28" t="n">
         <v>0.08</v>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="28" t="n">
         <v>0.09</v>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="28" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="28" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
@@ -1270,74 +1272,74 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1395,10 +1397,10 @@
           <t>Opening cash</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="12" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1408,10 +1410,10 @@
           <t>Operating cash flow</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="12" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1421,10 +1423,10 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="12" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1434,10 +1436,10 @@
           <t>Dividends</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="12" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1447,10 +1449,10 @@
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="12" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1460,10 +1462,10 @@
           <t>Debt issuance</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="28" t="n">
+      <c r="C10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1473,10 +1475,10 @@
           <t>Debt repayment</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1486,10 +1488,10 @@
           <t>Opening debt</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="12" t="n">
         <v>300</v>
       </c>
     </row>
@@ -1499,10 +1501,10 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="12" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1512,10 +1514,10 @@
           <t>Cash interest</t>
         </is>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="12" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1525,10 +1527,10 @@
           <t>Minimum cash</t>
         </is>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="12" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1538,10 +1540,10 @@
           <t>Maximum net leverage</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="30" t="n">
         <v>3.5</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -1551,10 +1553,10 @@
           <t>Minimum interest coverage</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="30" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1564,11 +1566,11 @@
           <t>Ending cash</t>
         </is>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="17">
         <f>C5+C6-C7-C8-C9+C10-C11</f>
         <v/>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="17">
         <f>D5+D6-D7-D8-D9+D10-D11</f>
         <v/>
       </c>
@@ -1579,11 +1581,11 @@
           <t>Ending debt</t>
         </is>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="17">
         <f>C12+C10-C11</f>
         <v/>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="17">
         <f>D12+D10-D11</f>
         <v/>
       </c>
@@ -1594,11 +1596,11 @@
           <t>Net debt</t>
         </is>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="17">
         <f>C22-C21</f>
         <v/>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="17">
         <f>D22-D21</f>
         <v/>
       </c>
@@ -1609,11 +1611,11 @@
           <t>Net leverage</t>
         </is>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>IFERROR(C23/C13,0)</f>
         <v/>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <f>IFERROR(D23/D13,0)</f>
         <v/>
       </c>
@@ -1624,11 +1626,11 @@
           <t>Interest coverage</t>
         </is>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <f>IFERROR(C13/C14,0)</f>
         <v/>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <f>IFERROR(D13/D14,0)</f>
         <v/>
       </c>
@@ -1639,11 +1641,11 @@
           <t>Financing gap</t>
         </is>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="17">
         <f>MAX(0,C15-C21)</f>
         <v/>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="17">
         <f>MAX(0,D15-D21)</f>
         <v/>
       </c>
@@ -1654,11 +1656,11 @@
           <t>Post-capex free cash flow</t>
         </is>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="17">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="17">
         <f>D6-D7</f>
         <v/>
       </c>
@@ -1669,11 +1671,11 @@
           <t>Shareholder distributions</t>
         </is>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="17">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="17">
         <f>D8+D9</f>
         <v/>
       </c>
@@ -1734,11 +1736,11 @@
           <t>Operating cash flow</t>
         </is>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="17">
         <f>'Treasury &amp; Liquidity'!C6</f>
         <v/>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="17">
         <f>'Treasury &amp; Liquidity'!D6</f>
         <v/>
       </c>
@@ -1754,11 +1756,11 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="17">
         <f>'Treasury &amp; Liquidity'!C7</f>
         <v/>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="17">
         <f>'Treasury &amp; Liquidity'!D7</f>
         <v/>
       </c>
@@ -1774,11 +1776,11 @@
           <t>Dividends</t>
         </is>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="17">
         <f>'Treasury &amp; Liquidity'!C8</f>
         <v/>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="17">
         <f>'Treasury &amp; Liquidity'!D8</f>
         <v/>
       </c>
@@ -1794,11 +1796,11 @@
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="17">
         <f>'Treasury &amp; Liquidity'!C9</f>
         <v/>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="17">
         <f>'Treasury &amp; Liquidity'!D9</f>
         <v/>
       </c>
@@ -1814,11 +1816,11 @@
           <t>Debt repayment</t>
         </is>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="17">
         <f>'Treasury &amp; Liquidity'!C11</f>
         <v/>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="17">
         <f>'Treasury &amp; Liquidity'!D11</f>
         <v/>
       </c>
@@ -1834,11 +1836,11 @@
           <t>Debt issuance</t>
         </is>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="17">
         <f>'Treasury &amp; Liquidity'!C10</f>
         <v/>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="17">
         <f>'Treasury &amp; Liquidity'!D10</f>
         <v/>
       </c>
@@ -1854,11 +1856,11 @@
           <t>Distribution funding residual</t>
         </is>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="17">
         <f>MAX(0,C7+C8-C5+C6)</f>
         <v/>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="17">
         <f>MAX(0,D7+D8-D5+D6)</f>
         <v/>
       </c>
@@ -1869,11 +1871,11 @@
           <t>Cash rollforward residual</t>
         </is>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="17">
         <f>'Treasury &amp; Liquidity'!C21-('Treasury &amp; Liquidity'!C5+'Treasury &amp; Liquidity'!C6-'Treasury &amp; Liquidity'!C7-'Treasury &amp; Liquidity'!C8-'Treasury &amp; Liquidity'!C9+'Treasury &amp; Liquidity'!C10-'Treasury &amp; Liquidity'!C11)</f>
         <v/>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="17">
         <f>'Treasury &amp; Liquidity'!D21-('Treasury &amp; Liquidity'!D5+'Treasury &amp; Liquidity'!D6-'Treasury &amp; Liquidity'!D7-'Treasury &amp; Liquidity'!D8-'Treasury &amp; Liquidity'!D9+'Treasury &amp; Liquidity'!D10-'Treasury &amp; Liquidity'!D11)</f>
         <v/>
       </c>
@@ -1934,11 +1936,11 @@
           <t>Ending cash</t>
         </is>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="17">
         <f>'Treasury &amp; Liquidity'!C21</f>
         <v/>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="17">
         <f>'Treasury &amp; Liquidity'!D21</f>
         <v/>
       </c>
@@ -1954,11 +1956,11 @@
           <t>Net leverage</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>'Treasury &amp; Liquidity'!C24</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>'Treasury &amp; Liquidity'!D24</f>
         <v/>
       </c>
@@ -1974,11 +1976,11 @@
           <t>Interest coverage</t>
         </is>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>'Treasury &amp; Liquidity'!C25</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>'Treasury &amp; Liquidity'!D25</f>
         <v/>
       </c>
@@ -1994,11 +1996,11 @@
           <t>Financing gap</t>
         </is>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="17">
         <f>'Treasury &amp; Liquidity'!C26</f>
         <v/>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="17">
         <f>'Treasury &amp; Liquidity'!D26</f>
         <v/>
       </c>
@@ -2014,11 +2016,11 @@
           <t>Distribution funding residual</t>
         </is>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="17">
         <f>'Capital Allocation'!C13</f>
         <v/>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="17">
         <f>'Capital Allocation'!D13</f>
         <v/>
       </c>
@@ -2084,11 +2086,11 @@
           <t>Cash rollforward residual</t>
         </is>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <f>'Capital Allocation'!D14</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>IF(ABS(C5)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -2104,11 +2106,11 @@
           <t>Debt rollforward residual</t>
         </is>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>'Treasury &amp; Liquidity'!D22-('Treasury &amp; Liquidity'!D12+'Treasury &amp; Liquidity'!D10-'Treasury &amp; Liquidity'!D11)</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="29">
         <f>IF(ABS(C6)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -2124,11 +2126,11 @@
           <t>Minimum cash</t>
         </is>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>'Treasury &amp; Liquidity'!D21-'Treasury &amp; Liquidity'!D15</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <f>IF(C7&gt;=0,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -2144,11 +2146,11 @@
           <t>Net leverage</t>
         </is>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>'Treasury &amp; Liquidity'!D24</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>IF(C8&lt;='Treasury &amp; Liquidity'!D16,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -2164,11 +2166,11 @@
           <t>Interest coverage</t>
         </is>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>'Treasury &amp; Liquidity'!D25</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="29">
         <f>IF(C9&gt;='Treasury &amp; Liquidity'!D17,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -2184,11 +2186,11 @@
           <t>Distribution funding</t>
         </is>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>'Capital Allocation'!D13</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <f>IF(C10&lt;0.01,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -2204,7 +2206,7 @@
           <t>Overall model status</t>
         </is>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>IF(COUNTIF(D5:D10,"FAIL")+COUNTIF(D5:D10,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D10,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v/>
       </c>
@@ -2231,125 +2233,125 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="33" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Corporate Finance — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Corporate Finance</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>tools/builders/build_corporate_finance_release.py</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>treasury, CFO staff, ALCO and board finance committee</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>liquidity and capital-allocation pack</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>weekly treasury; monthly ALCO; quarterly board</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="37" t="inlineStr">
+      <c r="F13" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2441,34 +2443,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="37" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="37" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="37" t="inlineStr">
+      <c r="F21" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2560,34 +2562,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="37" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="37" t="inlineStr">
+      <c r="E29" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="37" t="inlineStr">
+      <c r="F29" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2679,34 +2681,34 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="37" t="inlineStr">
+      <c r="C37" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="37" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="37" t="inlineStr">
+      <c r="E37" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="37" t="inlineStr">
+      <c r="F37" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2798,34 +2800,34 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="37" t="inlineStr">
+      <c r="D45" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="37" t="inlineStr">
+      <c r="E45" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="37" t="inlineStr">
+      <c r="F45" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2917,34 +2919,34 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="36" t="inlineStr">
+      <c r="B52" s="37" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="37" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C53" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="37" t="inlineStr">
+      <c r="D53" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="37" t="inlineStr">
+      <c r="E53" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="37" t="inlineStr">
+      <c r="F53" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3036,34 +3038,34 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="36" t="inlineStr">
+      <c r="B60" s="37" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="37" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C61" s="38" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="37" t="inlineStr">
+      <c r="D61" s="38" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="37" t="inlineStr">
+      <c r="E61" s="38" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="37" t="inlineStr">
+      <c r="F61" s="38" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
@@ -3177,49 +3179,49 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="33" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="38" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="38" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="38" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
@@ -3352,54 +3354,54 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="33" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="38" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="38" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="38" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3944,19 +3946,19 @@
       <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <f>E5*(1+Assumptions!C5)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <f>F5*(1+Assumptions!D5)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <f>G5*(1+Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <f>H5*(1+Assumptions!F5)</f>
         <v/>
       </c>
@@ -3967,28 +3969,28 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13">
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14">
         <f>IFERROR(D5/C5-1,"-")</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>IFERROR(E5/D5-1,"-")</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>IFERROR(F5/E5-1,"-")</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>IFERROR(G5/F5-1,"-")</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>IFERROR(H5/G5-1,"-")</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>IFERROR(I5/H5-1,"-")</f>
         <v/>
       </c>
@@ -4002,19 +4004,19 @@
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>F5*(1-Assumptions!C6)</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>G5*(1-Assumptions!D6)</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <f>H5*(1-Assumptions!E6)</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <f>I5*(1-Assumptions!F6)</f>
         <v/>
       </c>
@@ -4025,28 +4027,31 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12">
+      <c r="C8" s="13">
+        <f>C5-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="13">
         <f>D5-D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5-E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5-F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5-G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>H5-H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <f>I5-I7</f>
         <v/>
       </c>
@@ -4057,28 +4062,31 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13">
+      <c r="C9" s="14">
+        <f>IFERROR(C8/C5,"-")</f>
+        <v/>
+      </c>
+      <c r="D9" s="14">
         <f>IFERROR(D8/D5,"-")</f>
         <v/>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <f>IFERROR(E8/E5,"-")</f>
         <v/>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>IFERROR(F8/F5,"-")</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>IFERROR(G8/G5,"-")</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f>IFERROR(H8/H5,"-")</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="14">
         <f>IFERROR(I8/I5,"-")</f>
         <v/>
       </c>
@@ -4092,19 +4100,19 @@
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F5*Assumptions!C7</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G5*Assumptions!D7</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <f>H5*Assumptions!E7</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <f>I5*Assumptions!F7</f>
         <v/>
       </c>
@@ -4115,22 +4123,31 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12">
+      <c r="C11" s="13">
+        <f>C8-C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="13">
+        <f>D8-D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="13">
+        <f>E8-E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
         <f>F8-F10</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>G8-G10</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <f>H8-H10</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <f>I8-I10</f>
         <v/>
       </c>
@@ -4141,22 +4158,31 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13">
+      <c r="C12" s="14">
+        <f>IFERROR(C11/C5,"-")</f>
+        <v/>
+      </c>
+      <c r="D12" s="14">
+        <f>IFERROR(D11/D5,"-")</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>IFERROR(E11/E5,"-")</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
         <f>IFERROR(F11/F5,"-")</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>IFERROR(G11/G5,"-")</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <f>IFERROR(H11/H5,"-")</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="14">
         <f>IFERROR(I11/I5,"-")</f>
         <v/>
       </c>
@@ -4170,19 +4196,19 @@
       <c r="C13" s="12" t="n"/>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>F5*Assumptions!C10*Assumptions!C9</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>G5*Assumptions!D10*Assumptions!D9</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>H5*Assumptions!E10*Assumptions!E9</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <f>I5*Assumptions!F10*Assumptions!F9</f>
         <v/>
       </c>
@@ -4193,22 +4219,31 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12">
+      <c r="C14" s="13">
+        <f>C11-C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>D11-D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="13">
+        <f>E11-E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="13">
         <f>F11-F13</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>G11-G13</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <f>H11-H13</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <f>I11-I13</f>
         <v/>
       </c>
@@ -4222,19 +4257,19 @@
       <c r="C15" s="12" t="n"/>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
@@ -4245,22 +4280,31 @@
           <t>Pre-tax income</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12">
+      <c r="C16" s="13">
+        <f>C14-C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="13">
+        <f>D14-D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="13">
+        <f>E14-E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="13">
         <f>F14-F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>G14-G15</f>
         <v/>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <f>H14-H15</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <f>I14-I15</f>
         <v/>
       </c>
@@ -4274,19 +4318,19 @@
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <f>F16*Assumptions!C8</f>
         <v/>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <f>G16*Assumptions!D8</f>
         <v/>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <f>H16*Assumptions!E8</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <f>I16*Assumptions!F8</f>
         <v/>
       </c>
@@ -4297,22 +4341,31 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12">
+      <c r="C18" s="13">
+        <f>C16-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="13">
+        <f>D16-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="13">
+        <f>E16-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="13">
         <f>F16-F17</f>
         <v/>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <f>G16-G17</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <f>H16-H17</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <f>I16-I17</f>
         <v/>
       </c>
@@ -4323,22 +4376,22 @@
           <t>Diluted shares</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12">
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="13">
         <f>Assumptions!C12</f>
         <v/>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <f>Assumptions!D12</f>
         <v/>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <f>Assumptions!E12</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <f>Assumptions!F12</f>
         <v/>
       </c>
@@ -4349,22 +4402,31 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12">
+      <c r="C20" s="13">
+        <f>IFERROR(C18/C19,"-")</f>
+        <v/>
+      </c>
+      <c r="D20" s="13">
+        <f>IFERROR(D18/D19,"-")</f>
+        <v/>
+      </c>
+      <c r="E20" s="13">
+        <f>IFERROR(E18/E19,"-")</f>
+        <v/>
+      </c>
+      <c r="F20" s="13">
         <f>IFERROR(F18/F19,"-")</f>
         <v/>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <f>IFERROR(G18/G19,"-")</f>
         <v/>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <f>IFERROR(H18/H19,"-")</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <f>IFERROR(I18/I19,"-")</f>
         <v/>
       </c>
@@ -4438,11 +4500,11 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -4450,11 +4512,11 @@
           <t>Accounts receivable</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -4462,11 +4524,11 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -4474,23 +4536,23 @@
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -4501,11 +4563,11 @@
           <t>PP&amp;E net</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -4513,11 +4575,11 @@
           <t>Goodwill &amp; intangibles</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -4525,23 +4587,23 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <f>C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <f>D8+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>G8+G9+G10</f>
         <v/>
       </c>
@@ -4552,11 +4614,11 @@
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -4564,11 +4626,11 @@
           <t>Debt (current)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -4576,23 +4638,23 @@
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="13">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <f>E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>G12+G13</f>
         <v/>
       </c>
@@ -4603,11 +4665,11 @@
           <t>Long-term debt</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -4615,23 +4677,23 @@
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="13">
         <f>C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="13">
         <f>D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <f>E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>G14+G15</f>
         <v/>
       </c>
@@ -4642,35 +4704,35 @@
           <t>Total equity</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Balance check (Total assets - Total liabilities - Total equity, should = 0)</t>
         </is>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="17">
         <f>C11-C16-C17</f>
         <v/>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="17">
         <f>D11-D16-D17</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="17">
         <f>E11-E16-E17</f>
         <v/>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="17">
         <f>F11-F16-F17</f>
         <v/>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="17">
         <f>G11-G16-G17</f>
         <v/>
       </c>
@@ -4744,17 +4806,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="16">
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="18">
         <f>IS!F18</f>
         <v/>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="18">
         <f>IS!G18</f>
         <v/>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="18">
         <f>IS!H18</f>
         <v/>
       </c>
@@ -4765,17 +4827,17 @@
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="16">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="18">
         <f>IS!F13</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="18">
         <f>IS!G13</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="18">
         <f>IS!H13</f>
         <v/>
       </c>
@@ -4786,11 +4848,11 @@
           <t>+/- Change in NWC</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -4798,23 +4860,23 @@
           <t>Cash flow from operations</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -4825,11 +4887,11 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -4837,23 +4899,23 @@
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="13">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G8+G9</f>
         <v/>
       </c>
@@ -4864,11 +4926,11 @@
           <t>Debt issuance/(repayment)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -4876,11 +4938,11 @@
           <t>Dividends/buybacks</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -4888,23 +4950,23 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="13">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>G10+G11+G12</f>
         <v/>
       </c>
@@ -4980,23 +5042,23 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="19">
         <f>IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="19">
         <f>IS!G14*(1-Assumptions!D8)+IS!G13-IS!G5*Assumptions!D10</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="19">
         <f>IS!H14*(1-Assumptions!E8)+IS!H13-IS!H5*Assumptions!E10</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="19">
         <f>IS!I14*(1-Assumptions!F8)+IS!I13-IS!I5*Assumptions!F10</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="19">
         <f>F5*(1+Assumptions!G5)</f>
         <v/>
       </c>
@@ -5005,7 +5067,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="20" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5015,23 +5077,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="21">
         <f>1/(1+$I$5)^(1)</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="21">
         <f>1/(1+$I$5)^(2)</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="21">
         <f>1/(1+$I$5)^(3)</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="21">
         <f>1/(1+$I$5)^(4)</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="21">
         <f>1/(1+$I$5)^(5)</f>
         <v/>
       </c>
@@ -5040,7 +5102,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="20" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -5050,23 +5112,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="22">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f>F5*F6</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <f>G5*G6</f>
         <v/>
       </c>
@@ -5075,7 +5137,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="22">
         <f>G5*(1+I6)/(I5-I6)</f>
         <v/>
       </c>
@@ -5086,7 +5148,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="22">
         <f>I7*G6</f>
         <v/>
       </c>
@@ -5097,7 +5159,7 @@
           <t>Sum PV of FCF</t>
         </is>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="22">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
@@ -5108,7 +5170,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="23">
         <f>I8+I9</f>
         <v/>
       </c>
@@ -5119,7 +5181,7 @@
           <t>Less: net debt</t>
         </is>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5129,7 +5191,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="23">
         <f>I10-I11</f>
         <v/>
       </c>
@@ -5140,7 +5202,7 @@
           <t>Diluted shares (mm)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5150,7 +5212,7 @@
           <t>Implied value/share</t>
         </is>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="23">
         <f>I12/I13</f>
         <v/>
       </c>
